--- a/outputs/evaluation/architecture/validation/gemini-3-5/CF_M06/run_1/CF_M06_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/gemini-3-5/CF_M06/run_1/CF_M06_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.6111</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.5641</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.6897</v>
       </c>
       <c r="D3" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.975</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.2857</v>
       </c>
       <c r="D4" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8120000000000001</v>
       </c>
     </row>
@@ -1201,7 +1215,6 @@
       <c r="D2" t="n">
         <v>0.8071</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1222,7 +1235,6 @@
           <t>['AU_06', 'AU_07']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_34</t>
@@ -1233,7 +1245,6 @@
           <t>dispositiu mòbil, servidor waapiti</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1252,7 +1263,6 @@
           <t>CF_M06_AU01, CF_M06_AU02</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M06_AU27</t>
@@ -1283,7 +1293,6 @@
       <c r="D3" t="n">
         <v>0.8169999999999999</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1304,7 +1313,6 @@
           <t>['AU_07', 'AU_26']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_35</t>
@@ -1315,7 +1323,6 @@
           <t>servidor waapiti, aws</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1334,7 +1341,6 @@
           <t>CF_M06_AU02, CF_M06_AU05</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M06_AU28</t>
@@ -1390,13 +1396,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Observer Pattern</t>
@@ -1420,13 +1424,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M06_P03</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1467,14 +1469,11 @@
           <t>48</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>P_05</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Decorator Pattern</t>
@@ -1498,13 +1497,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M06_P04</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1545,14 +1542,11 @@
           <t>44</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Waapiti Server</t>
@@ -1571,14 +1565,11 @@
       <c r="P6" t="n">
         <v>45</v>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M06_AU02</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1624,13 +1615,11 @@
           <t>['AU_28']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_30</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Apple Push Notification Service</t>
@@ -1649,14 +1638,11 @@
       <c r="P7" t="n">
         <v>91</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M06_AU21</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1702,13 +1688,11 @@
           <t>['AU_28']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_29</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Firebase Cloud Messaging</t>
@@ -1727,14 +1711,11 @@
       <c r="P8" t="n">
         <v>91</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M06_AU20</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1775,14 +1756,11 @@
           <t>50</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>React Native</t>
@@ -1806,13 +1784,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M06_AU06</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1853,14 +1829,11 @@
           <t>50</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>React</t>
@@ -1884,13 +1857,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M06_AU14</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1931,14 +1902,11 @@
           <t>48</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>P_06</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Lazy Loading</t>
@@ -1962,13 +1930,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M06_P05</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2009,14 +1975,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Dispatcher</t>
@@ -2040,13 +2003,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M06_AU09</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2087,14 +2048,11 @@
           <t>50</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Jest</t>
@@ -2118,13 +2076,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M06_AU16</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2170,13 +2126,11 @@
           <t>['AU_34']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_27</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2200,13 +2154,11 @@
           <t>CF_M06_AU26</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M06_AU29</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2247,14 +2199,11 @@
           <t>45, 46</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Store</t>
@@ -2278,13 +2227,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M06_AU07</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2325,14 +2272,11 @@
           <t>50</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Expo</t>
@@ -2356,13 +2300,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M06_AU15</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2403,14 +2345,11 @@
           <t>50</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_19</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>NodeJS</t>
@@ -2429,14 +2368,11 @@
       <c r="P17" t="n">
         <v>51</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M06_AU17</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2477,14 +2413,11 @@
           <t>51</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_21</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>NestJS</t>
@@ -2503,14 +2436,11 @@
       <c r="P18" t="n">
         <v>51</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M06_AU19</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2556,13 +2486,11 @@
           <t>['AU_28']</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_32</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>AWS SNS</t>
@@ -2581,14 +2509,11 @@
       <c r="P19" t="n">
         <v>92</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M06_AU22</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2629,14 +2554,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Flux</t>
@@ -2660,13 +2582,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2712,13 +2632,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Redux</t>
@@ -2742,13 +2660,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M06_AU25</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2789,14 +2705,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Action</t>
@@ -2820,13 +2733,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M06_AU08</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2867,14 +2778,11 @@
           <t>50, 51</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_20</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>TypeScript</t>
@@ -2893,14 +2801,11 @@
       <c r="P23" t="n">
         <v>51</v>
       </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M06_AU18</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2974,7 +2879,6 @@
           <t>Clients</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>L’empresa té dues vies de negoci. D’una banda els clients finals, el qual actua com a consultoria per tal de satisfer les necessitats del client: tipus de contingut i tecnologia a implementar.</t>
@@ -3010,7 +2914,6 @@
           <t>Partners</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>D’altra banda, treballa với partners, que essencialment són empreses de tercers que disposen dels seus propis clients i els hi ofereixen solucions de senyalització digital mitjançant la tecnologia de Waapiti.</t>
@@ -3046,7 +2949,6 @@
           <t>Players</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Players: són equips informàtics que fan la funció d’intermediari entre la plataforma de Waapiti i el suport audiovisual en si, permetent així la sincronització i reproducció dels continguts dels clients.</t>
@@ -3082,7 +2984,6 @@
           <t>Software</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Per tal d’establir aquesta comunicació l’empresa instal·la un software propi en aquests players, que està preparat per donar suport a múltiples tipologies de players.</t>
@@ -3118,7 +3019,6 @@
           <t>Waapiti</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Waapiti és una empresa tecnològica que es dedica en aquest àmbit.</t>
@@ -3154,7 +3054,6 @@
           <t>Dispositiu mòbil</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>L’arquitectura física de la solució està format per un dispositiu mòbil, ja sigui sistema iOS o Android, i el servidor de l’empresa.</t>
@@ -3190,7 +3089,6 @@
           <t>Presentació</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Presentació: és la capa que es comunica amb l’usuari.</t>
@@ -3226,7 +3124,6 @@
           <t>Domini</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Domini: és la capa que conté la lògica de negoci.</t>
@@ -3262,7 +3159,6 @@
           <t>Dades</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Dades: és la capa que conté la informació.</t>
@@ -3298,7 +3194,6 @@
           <t>Reducers</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Els Reducers són funcions pures que reben l’estat actual de l’aplicació i l’acció a realitzar i retornen un nou estat, sense modificar directament l’estat actual.</t>
@@ -3334,7 +3229,6 @@
           <t>Visual Studio Code</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Visual Studio Code: és un editor de font desenvolupar per Microsoft.</t>
@@ -3370,7 +3264,6 @@
           <t>GIT</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>GIT: és un sistema de control de versions de codi font.</t>
@@ -3406,7 +3299,6 @@
           <t>React Navigation</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>En primer lloc, per a la navegació s’utilitza la llibreria React Navigation, que ofereix la transició entre pantalles de forma senzilla i un historial de navegació.</t>
@@ -3442,7 +3334,6 @@
           <t>react-native-async-storage</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Per a la gestió de la sessió s’utilitza la llibreria react-native-async-storage, que ens permet guardar parells de clau-valor de manera local en els dispositius.</t>
@@ -3478,7 +3369,6 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>És el servidor que s’encarrega de comunicar-se amb la base de dades i altres serveis allotjats a AWS.</t>
@@ -3514,7 +3404,6 @@
           <t>Push Notification Service</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Així mateix es necessita un servei de notificacions que es comuniqui amb aquestes.</t>
@@ -3550,7 +3439,6 @@
           <t>Expo Push API</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Expo Push API: Expo Push API és un servei que facilita la implementació de les notificacions push ja que es delega toda la configuració al servei.</t>
@@ -3581,7 +3469,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>players, software</t>
@@ -3617,7 +3504,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>push notification service, dispositiu mòbil</t>
@@ -3658,7 +3544,6 @@
           <t>3 Layers</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Aquesta arquitectura segueix el model de 3 capes: Presentació, Domini, Dades.</t>
@@ -3750,7 +3635,6 @@
           <t>Mobile device</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>This is the device where the application will be hosted.</t>
@@ -3786,7 +3670,6 @@
           <t>Presentation</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>This is the layer that communicates with the user. This is where the system data is displayed and the data entered by the user is collected.</t>
@@ -3822,7 +3705,6 @@
           <t>Domain</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>This is the layer that contains the business logic. In this layer, the information is processed or the operations necessary for the system to function correctly are performed</t>
@@ -3858,7 +3740,6 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>this is the layer that contains the information.</t>
@@ -3889,7 +3770,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>action, store</t>
@@ -3925,7 +3805,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>dispatcher, store</t>
@@ -3941,7 +3820,6 @@
           <t>AU_36</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>0.6706</v>
       </c>
@@ -3962,7 +3840,6 @@
           <t>User</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>As already mentioned, there are third-party companies that offer digital signage consulting using Waapiti technology. They are end users of this project.</t>
@@ -3993,7 +3870,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>presentation, user</t>
@@ -4034,7 +3910,6 @@
           <t>Mobile Application</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>The project “Development of a mobile application for a digital signage company”</t>
@@ -4070,7 +3945,6 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t xml:space="preserve">these are computer equipment that act as an intermediary between the Waapiti platform and the audiovisual media itself, thus allowing the synchronization or reproduction of client
@@ -4102,7 +3976,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>waapiti server, mobile application</t>
@@ -4139,7 +4012,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>mobile application, waapiti server</t>
@@ -4180,7 +4052,6 @@
           <t>Socket</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>the content according to the messages that it sends.</t>
@@ -4216,7 +4087,6 @@
           <t>Three Layers</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>This architecture follows the 3-layer model</t>
